--- a/public/documents/pieces-defense/RF-tables-trop-nombreuses.xlsx
+++ b/public/documents/pieces-defense/RF-tables-trop-nombreuses.xlsx
@@ -4641,7 +4641,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>NON — aucune table</t>
+          <t>NON, aucune table</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>NON — aucune table</t>
+          <t>NON, aucune table</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>NON — aucune table</t>
+          <t>NON, aucune table</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>NON — aucune table</t>
+          <t>NON, aucune table</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -4730,64 +4730,64 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>n°100</t>
+          <t>n°101 à 117 (sauf 102)</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Extérieur, le soir uniquement</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Pas de parasol, très rarement</t>
-        </is>
-      </c>
+          <t>Oui (terrasse)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>n°101 à 124</t>
+          <t>n°102</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Oui (terrasse)</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
+          <t>NON, aucune table</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>N'existe pas</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>n°116 et 117</t>
+          <t>n°125</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Terrasse, 14 juillet et 31 déc. au soir</t>
+          <t>NON, aucune table</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Pas de parasol sinon</t>
+          <t>N'existe pas</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>n°125</t>
+          <t>n°116 et 117</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>NON — aucune table</t>
+          <t>Terrasse, occasionnelle</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>N'existe pas</t>
+          <t>Jours de forte affluence</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Exemple daté : table réelle scindée en plusieurs notes — 2022-05-14</t>
+          <t>Exemple daté : table réelle scindée en plusieurs notes : 2022-05-14</t>
         </is>
       </c>
     </row>
